--- a/products/Catering_Business_Manager_BASIC_Fresh.xlsx
+++ b/products/Catering_Business_Manager_BASIC_Fresh.xlsx
@@ -4389,11 +4389,11 @@
         <v>1</v>
       </c>
       <c r="I2" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=1)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=1)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=1)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=1)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K2" s="1">
@@ -4436,11 +4436,11 @@
         <v>2</v>
       </c>
       <c r="I3" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=2)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=2)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=2)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=2)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K3" s="1">
@@ -4483,11 +4483,11 @@
         <v>3</v>
       </c>
       <c r="I4" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=3)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=3)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=3)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=3)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K4" s="1">
@@ -4530,11 +4530,11 @@
         <v>4</v>
       </c>
       <c r="I5" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=4)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=4)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=4)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=4)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K5" s="1">
@@ -4577,11 +4577,11 @@
         <v>5</v>
       </c>
       <c r="I6" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=5)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=5)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=5)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=5)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K6" s="1">
@@ -4624,11 +4624,11 @@
         <v>6</v>
       </c>
       <c r="I7" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=6)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=6)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=6)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=6)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K7" s="1">
@@ -4671,11 +4671,11 @@
         <v>7</v>
       </c>
       <c r="I8" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=7)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=7)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=7)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=7)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K8" s="1">
@@ -4718,11 +4718,11 @@
         <v>8</v>
       </c>
       <c r="I9" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=8)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=8)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=8)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=8)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K9" s="1">
@@ -4765,11 +4765,11 @@
         <v>9</v>
       </c>
       <c r="I10" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=9)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=9)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=9)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=9)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K10" s="1">
@@ -4812,11 +4812,11 @@
         <v>10</v>
       </c>
       <c r="I11" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=10)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=10)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=10)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=10)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K11" s="1">
@@ -4859,11 +4859,11 @@
         <v>11</v>
       </c>
       <c r="I12" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=11)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=11)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=11)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=11)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K12" s="1">
@@ -4906,11 +4906,11 @@
         <v>12</v>
       </c>
       <c r="I13" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=12)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=12)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=12)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=12)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K13" s="1">
@@ -5267,11 +5267,11 @@
     <row r="26" spans="14:32">
       <c r="Q26" s="1">
         <f>IF('👥 Clients'!$C$8="","",'👥 Clients'!$C$8)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R26" s="1">
         <f>IF($Q26="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q26,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA26" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),25),"")</f>
@@ -5301,11 +5301,11 @@
       </c>
       <c r="Q27" s="1">
         <f>IF('👥 Clients'!$C$9="","",'👥 Clients'!$C$9)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R27" s="1">
         <f>IF($Q27="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q27,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA27" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),26),"")</f>
@@ -5336,11 +5336,11 @@
       </c>
       <c r="Q28" s="1">
         <f>IF('👥 Clients'!$C$10="","",'👥 Clients'!$C$10)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R28" s="1">
         <f>IF($Q28="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q28,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA28" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),27),"")</f>
@@ -5371,11 +5371,11 @@
       </c>
       <c r="Q29" s="1">
         <f>IF('👥 Clients'!$C$11="","",'👥 Clients'!$C$11)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R29" s="1">
         <f>IF($Q29="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q29,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA29" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),28),"")</f>
@@ -5406,11 +5406,11 @@
       </c>
       <c r="Q30" s="1">
         <f>IF('👥 Clients'!$C$12="","",'👥 Clients'!$C$12)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R30" s="1">
         <f>IF($Q30="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q30,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA30" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),29),"")</f>
@@ -5441,11 +5441,11 @@
       </c>
       <c r="Q31" s="1">
         <f>IF('👥 Clients'!$C$13="","",'👥 Clients'!$C$13)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R31" s="1">
         <f>IF($Q31="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q31,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA31" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),30),"")</f>
@@ -5477,11 +5477,11 @@
       </c>
       <c r="Q32" s="1">
         <f>IF('👥 Clients'!$C$14="","",'👥 Clients'!$C$14)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R32" s="1">
         <f>IF($Q32="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q32,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA32" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),31),"")</f>
@@ -5513,11 +5513,11 @@
       </c>
       <c r="Q33" s="1">
         <f>IF('👥 Clients'!$C$15="","",'👥 Clients'!$C$15)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R33" s="1">
         <f>IF($Q33="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q33,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA33" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),32),"")</f>
@@ -5541,11 +5541,11 @@
     <row r="34" spans="14:32">
       <c r="Q34" s="1">
         <f>IF('👥 Clients'!$C$16="","",'👥 Clients'!$C$16)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R34" s="1">
         <f>IF($Q34="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q34,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA34" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),33),"")</f>
@@ -5569,11 +5569,11 @@
     <row r="35" spans="14:32">
       <c r="Q35" s="1">
         <f>IF('👥 Clients'!$C$17="","",'👥 Clients'!$C$17)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R35" s="1">
         <f>IF($Q35="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q35,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA35" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),34),"")</f>
@@ -5598,11 +5598,11 @@
     <row r="36" spans="14:32">
       <c r="Q36" s="1">
         <f>IF('👥 Clients'!$C$18="","",'👥 Clients'!$C$18)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R36" s="1">
         <f>IF($Q36="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q36,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA36" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),35),"")</f>
@@ -5627,11 +5627,11 @@
     <row r="37" spans="14:32">
       <c r="Q37" s="1">
         <f>IF('👥 Clients'!$C$19="","",'👥 Clients'!$C$19)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R37" s="1">
         <f>IF($Q37="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q37,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA37" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),36),"")</f>
@@ -5649,11 +5649,11 @@
     <row r="38" spans="14:32">
       <c r="Q38" s="1">
         <f>IF('👥 Clients'!$C$20="","",'👥 Clients'!$C$20)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R38" s="1">
         <f>IF($Q38="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q38,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA38" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),37),"")</f>
@@ -5671,11 +5671,11 @@
     <row r="39" spans="14:32">
       <c r="Q39" s="1">
         <f>IF('👥 Clients'!$C$21="","",'👥 Clients'!$C$21)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R39" s="1">
         <f>IF($Q39="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q39,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA39" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),38),"")</f>
@@ -5693,11 +5693,11 @@
     <row r="40" spans="14:32">
       <c r="Q40" s="1">
         <f>IF('👥 Clients'!$C$22="","",'👥 Clients'!$C$22)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R40" s="1">
         <f>IF($Q40="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q40,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA40" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),39),"")</f>
@@ -5725,7 +5725,7 @@
     </row>
     <row r="42" spans="14:32">
       <c r="AA42" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),1),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),1),"")</f>
         <v/>
       </c>
       <c r="AB42" s="1">
@@ -5734,12 +5734,12 @@
       </c>
       <c r="AC42" s="1">
         <f>IF($AA42="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA42,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="43" spans="14:32">
       <c r="AA43" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),2),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),2),"")</f>
         <v/>
       </c>
       <c r="AB43" s="1">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="AC43" s="1">
         <f>IF($AA43="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA43,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="44" spans="14:32">
       <c r="AA44" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),3),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),3),"")</f>
         <v/>
       </c>
       <c r="AB44" s="1">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="AC44" s="1">
         <f>IF($AA44="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA44,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="45" spans="14:32">
       <c r="AA45" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),4),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),4),"")</f>
         <v/>
       </c>
       <c r="AB45" s="1">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="AC45" s="1">
         <f>IF($AA45="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA45,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="46" spans="14:32">
       <c r="AA46" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),5),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),5),"")</f>
         <v/>
       </c>
       <c r="AB46" s="1">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="AC46" s="1">
         <f>IF($AA46="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA46,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="47" spans="14:32">
       <c r="AA47" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),6),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),6),"")</f>
         <v/>
       </c>
       <c r="AB47" s="1">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="AC47" s="1">
         <f>IF($AA47="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA47,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="48" spans="14:32">
       <c r="AA48" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),7),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),7),"")</f>
         <v/>
       </c>
       <c r="AB48" s="1">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="AC48" s="1">
         <f>IF($AA48="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA48,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="49" spans="27:29">
       <c r="AA49" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),8),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),8),"")</f>
         <v/>
       </c>
       <c r="AB49" s="1">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="AC49" s="1">
         <f>IF($AA49="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA49,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="50" spans="27:29">
       <c r="AA50" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),9),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),9),"")</f>
         <v/>
       </c>
       <c r="AB50" s="1">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="AC50" s="1">
         <f>IF($AA50="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA50,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="51" spans="27:29">
       <c r="AA51" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),10),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),10),"")</f>
         <v/>
       </c>
       <c r="AB51" s="1">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="AC51" s="1">
         <f>IF($AA51="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA51,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="52" spans="27:29">
       <c r="AA52" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),11),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),11),"")</f>
         <v/>
       </c>
       <c r="AB52" s="1">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="AC52" s="1">
         <f>IF($AA52="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA52,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="53" spans="27:29">
       <c r="AA53" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),12),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),12),"")</f>
         <v/>
       </c>
       <c r="AB53" s="1">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="AC53" s="1">
         <f>IF($AA53="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA53,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="54" spans="27:29">
       <c r="AA54" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),13),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),13),"")</f>
         <v/>
       </c>
       <c r="AB54" s="1">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="AC54" s="1">
         <f>IF($AA54="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA54,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="55" spans="27:29">
       <c r="AA55" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),14),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),14),"")</f>
         <v/>
       </c>
       <c r="AB55" s="1">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="AC55" s="1">
         <f>IF($AA55="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA55,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="56" spans="27:29">
       <c r="AA56" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),15),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),15),"")</f>
         <v/>
       </c>
       <c r="AB56" s="1">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="AC56" s="1">
         <f>IF($AA56="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA56,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="57" spans="27:29">
       <c r="AA57" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),16),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),16),"")</f>
         <v/>
       </c>
       <c r="AB57" s="1">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="AC57" s="1">
         <f>IF($AA57="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA57,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="58" spans="27:29">
       <c r="AA58" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),17),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),17),"")</f>
         <v/>
       </c>
       <c r="AB58" s="1">
@@ -5958,12 +5958,12 @@
       </c>
       <c r="AC58" s="1">
         <f>IF($AA58="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA58,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="59" spans="27:29">
       <c r="AA59" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),18),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),18),"")</f>
         <v/>
       </c>
       <c r="AB59" s="1">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="AC59" s="1">
         <f>IF($AA59="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA59,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="60" spans="27:29">
       <c r="AA60" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),19),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),19),"")</f>
         <v/>
       </c>
       <c r="AB60" s="1">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="AC60" s="1">
         <f>IF($AA60="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA60,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="61" spans="27:29">
       <c r="AA61" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),20),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),20),"")</f>
         <v/>
       </c>
       <c r="AB61" s="1">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="AC61" s="1">
         <f>IF($AA61="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA61,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="62" spans="27:29">
       <c r="AA62" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),21),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),21),"")</f>
         <v/>
       </c>
       <c r="AB62" s="1">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="AC62" s="1">
         <f>IF($AA62="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA62,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="63" spans="27:29">
       <c r="AA63" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),22),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),22),"")</f>
         <v/>
       </c>
       <c r="AB63" s="1">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="AC63" s="1">
         <f>IF($AA63="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA63,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="64" spans="27:29">
       <c r="AA64" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),23),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),23),"")</f>
         <v/>
       </c>
       <c r="AB64" s="1">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="AC64" s="1">
         <f>IF($AA64="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA64,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="65" spans="27:29">
       <c r="AA65" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),24),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),24),"")</f>
         <v/>
       </c>
       <c r="AB65" s="1">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="AC65" s="1">
         <f>IF($AA65="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA65,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="66" spans="27:29">
       <c r="AA66" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),25),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),25),"")</f>
         <v/>
       </c>
       <c r="AB66" s="1">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="AC66" s="1">
         <f>IF($AA66="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA66,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="67" spans="27:29">
       <c r="AA67" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),26),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),26),"")</f>
         <v/>
       </c>
       <c r="AB67" s="1">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="AC67" s="1">
         <f>IF($AA67="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA67,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="68" spans="27:29">
       <c r="AA68" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),27),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),27),"")</f>
         <v/>
       </c>
       <c r="AB68" s="1">
@@ -6098,12 +6098,12 @@
       </c>
       <c r="AC68" s="1">
         <f>IF($AA68="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA68,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="69" spans="27:29">
       <c r="AA69" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),28),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),28),"")</f>
         <v/>
       </c>
       <c r="AB69" s="1">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="AC69" s="1">
         <f>IF($AA69="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA69,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="70" spans="27:29">
       <c r="AA70" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),29),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),29),"")</f>
         <v/>
       </c>
       <c r="AB70" s="1">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="AC70" s="1">
         <f>IF($AA70="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA70,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="71" spans="27:29">
       <c r="AA71" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),30),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),30),"")</f>
         <v/>
       </c>
       <c r="AB71" s="1">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="AC71" s="1">
         <f>IF($AA71="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA71,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="72" spans="27:29">
       <c r="AA72" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),31),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),31),"")</f>
         <v/>
       </c>
       <c r="AB72" s="1">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="AC72" s="1">
         <f>IF($AA72="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA72,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="73" spans="27:29">
       <c r="AA73" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),32),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),32),"")</f>
         <v/>
       </c>
       <c r="AB73" s="1">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="AC73" s="1">
         <f>IF($AA73="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA73,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="74" spans="27:29">
       <c r="AA74" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),33),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),33),"")</f>
         <v/>
       </c>
       <c r="AB74" s="1">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="AC74" s="1">
         <f>IF($AA74="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA74,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="75" spans="27:29">
       <c r="AA75" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),34),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),34),"")</f>
         <v/>
       </c>
       <c r="AB75" s="1">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="AC75" s="1">
         <f>IF($AA75="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA75,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="76" spans="27:29">
       <c r="AA76" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),35),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),35),"")</f>
         <v/>
       </c>
       <c r="AB76" s="1">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="AC76" s="1">
         <f>IF($AA76="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA76,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="77" spans="27:29">
       <c r="AA77" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),36),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),36),"")</f>
         <v/>
       </c>
       <c r="AB77" s="1">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="AC77" s="1">
         <f>IF($AA77="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA77,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="78" spans="27:29">
       <c r="AA78" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),37),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),37),"")</f>
         <v/>
       </c>
       <c r="AB78" s="1">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="AC78" s="1">
         <f>IF($AA78="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA78,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="79" spans="27:29">
       <c r="AA79" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),38),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),38),"")</f>
         <v/>
       </c>
       <c r="AB79" s="1">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="AC79" s="1">
         <f>IF($AA79="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA79,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="80" spans="27:29">
       <c r="AA80" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),39),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),39),"")</f>
         <v/>
       </c>
       <c r="AB80" s="1">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="AC80" s="1">
         <f>IF($AA80="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA80,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="81" spans="27:29">
       <c r="AA81" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),40),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),40),"")</f>
         <v/>
       </c>
       <c r="AB81" s="1">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="AC81" s="1">
         <f>IF($AA81="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA81,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="82" spans="27:29">
       <c r="AA82" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),41),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),41),"")</f>
         <v/>
       </c>
       <c r="AB82" s="1">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="AC82" s="1">
         <f>IF($AA82="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA82,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="83" spans="27:29">
       <c r="AA83" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),42),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),42),"")</f>
         <v/>
       </c>
       <c r="AB83" s="1">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="AC83" s="1">
         <f>IF($AA83="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA83,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="84" spans="27:29">
       <c r="AA84" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),43),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),43),"")</f>
         <v/>
       </c>
       <c r="AB84" s="1">
@@ -6322,12 +6322,12 @@
       </c>
       <c r="AC84" s="1">
         <f>IF($AA84="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA84,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="85" spans="27:29">
       <c r="AA85" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),44),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),44),"")</f>
         <v/>
       </c>
       <c r="AB85" s="1">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="AC85" s="1">
         <f>IF($AA85="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA85,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="86" spans="27:29">
       <c r="AA86" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),45),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),45),"")</f>
         <v/>
       </c>
       <c r="AB86" s="1">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="AC86" s="1">
         <f>IF($AA86="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA86,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="87" spans="27:29">
       <c r="AA87" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),46),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),46),"")</f>
         <v/>
       </c>
       <c r="AB87" s="1">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="AC87" s="1">
         <f>IF($AA87="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA87,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="88" spans="27:29">
       <c r="AA88" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),47),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),47),"")</f>
         <v/>
       </c>
       <c r="AB88" s="1">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="AC88" s="1">
         <f>IF($AA88="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA88,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="89" spans="27:29">
       <c r="AA89" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),48),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),48),"")</f>
         <v/>
       </c>
       <c r="AB89" s="1">
@@ -6392,12 +6392,12 @@
       </c>
       <c r="AC89" s="1">
         <f>IF($AA89="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA89,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="90" spans="27:29">
       <c r="AA90" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),49),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),49),"")</f>
         <v/>
       </c>
       <c r="AB90" s="1">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="AC90" s="1">
         <f>IF($AA90="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA90,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="91" spans="27:29">
       <c r="AA91" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),50),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),50),"")</f>
         <v/>
       </c>
       <c r="AB91" s="1">
@@ -6420,12 +6420,12 @@
       </c>
       <c r="AC91" s="1">
         <f>IF($AA91="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA91,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="92" spans="27:29">
       <c r="AA92" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),51),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),51),"")</f>
         <v/>
       </c>
       <c r="AB92" s="1">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="AC92" s="1">
         <f>IF($AA92="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA92,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="93" spans="27:29">
       <c r="AA93" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),52),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),52),"")</f>
         <v/>
       </c>
       <c r="AB93" s="1">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="AC93" s="1">
         <f>IF($AA93="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA93,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="94" spans="27:29">
       <c r="AA94" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),53),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),53),"")</f>
         <v/>
       </c>
       <c r="AB94" s="1">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="AC94" s="1">
         <f>IF($AA94="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA94,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="95" spans="27:29">
       <c r="AA95" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),54),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),54),"")</f>
         <v/>
       </c>
       <c r="AB95" s="1">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="AC95" s="1">
         <f>IF($AA95="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA95,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="96" spans="27:29">
       <c r="AA96" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),55),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),55),"")</f>
         <v/>
       </c>
       <c r="AB96" s="1">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="AC96" s="1">
         <f>IF($AA96="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA96,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="97" spans="27:29">
       <c r="AA97" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),56),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),56),"")</f>
         <v/>
       </c>
       <c r="AB97" s="1">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="AC97" s="1">
         <f>IF($AA97="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA97,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="98" spans="27:29">
       <c r="AA98" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),57),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),57),"")</f>
         <v/>
       </c>
       <c r="AB98" s="1">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="AC98" s="1">
         <f>IF($AA98="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA98,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="99" spans="27:29">
       <c r="AA99" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),58),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),58),"")</f>
         <v/>
       </c>
       <c r="AB99" s="1">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="AC99" s="1">
         <f>IF($AA99="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA99,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="100" spans="27:29">
       <c r="AA100" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),59),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),59),"")</f>
         <v/>
       </c>
       <c r="AB100" s="1">
@@ -6546,12 +6546,12 @@
       </c>
       <c r="AC100" s="1">
         <f>IF($AA100="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA100,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="101" spans="27:29">
       <c r="AA101" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),60),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),60),"")</f>
         <v/>
       </c>
       <c r="AB101" s="1">
@@ -6560,11 +6560,10 @@
       </c>
       <c r="AC101" s="1">
         <f>IF($AA101="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA101,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter>
@@ -7180,7 +7179,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="20">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G2:H2"/>
@@ -7394,7 +7392,7 @@
     </row>
     <row r="9" spans="2:16" ht="30" customHeight="1">
       <c r="B9" s="40">
-        <f>COUNTIF('📅 Events'!$Q$8:$Q$47,"&lt;&gt;❌ Cancelled")+COUNTIF('📅 Events'!$Q$8:$Q$47,"❌ Cancelled")</f>
+        <f>SUMPRODUCT(('📅 Events'!$Q$8:$Q$47&lt;&gt;"")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled"))</f>
         <v>0</v>
       </c>
       <c r="C9" s="40"/>
@@ -7690,7 +7688,6 @@
     <row r="89" ht="18" customHeight="1"/>
     <row r="90" ht="18" customHeight="1"/>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="46">
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="K2:P2"/>
@@ -8871,7 +8868,6 @@
       <c r="C56" s="30"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="18">
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B3:L3"/>
@@ -9024,7 +9020,7 @@
     <row r="4" spans="2:18" ht="7" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:18" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="48" t="str">
-        <f>"Bookings: "&amp;COUNTIF('📅 Events'!$Q$8:$Q$47,"&lt;&gt;❌ Cancelled")</f>
+        <f>"Bookings: "&amp;SUMPRODUCT(('📅 Events'!$Q$8:$Q$47&lt;&gt;"")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled"))</f>
         <v>Bookings: 0</v>
       </c>
       <c r="C5" s="48"/>
@@ -10347,30 +10343,30 @@
       <c r="E48" s="69"/>
       <c r="F48" s="69"/>
       <c r="G48" s="70">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$G$8:$G$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$G$8:$G$47)</f>
         <v>0</v>
       </c>
       <c r="H48" s="69"/>
       <c r="I48" s="70">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$I$8:$I$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$I$8:$I$47)</f>
         <v>0</v>
       </c>
       <c r="J48" s="69"/>
       <c r="K48" s="70">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$K$8:$K$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$K$8:$K$47)</f>
         <v>0</v>
       </c>
       <c r="L48" s="70">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$L$8:$L$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$L$8:$L$47)</f>
         <v>0</v>
       </c>
       <c r="M48" s="70">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$M$8:$M$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$M$8:$M$47)</f>
         <v>0</v>
       </c>
       <c r="N48" s="69"/>
       <c r="O48" s="70">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$O$8:$O$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$O$8:$O$47)</f>
         <v>0</v>
       </c>
       <c r="P48" s="70">
@@ -10455,7 +10451,6 @@
       <c r="Q55" s="30"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="18">
     <mergeCell ref="B2:O2"/>
     <mergeCell ref="B3:O3"/>
@@ -10787,7 +10782,7 @@
     <row r="23" spans="1:7" ht="21" customHeight="1"/>
     <row r="24" spans="1:7" ht="21" customHeight="1">
       <c r="B24" s="80">
-        <f>IF($E$16="","",Currency&amp;TEXT($E$16,"#,##0.00")&amp;"  for the event   ·   "&amp;Currency&amp;TEXT($E$17,"#,##0.00")&amp;" per guest")</f>
+        <f>IF($E$16="","",Currency&amp;TEXT($E$16,"#,##0.00")&amp;" for the event   ·   "&amp;Currency&amp;TEXT($E$17,"#,##0.00")&amp;" per guest")</f>
         <v/>
       </c>
       <c r="C24" s="80"/>
@@ -10890,7 +10885,6 @@
     </row>
     <row r="36" spans="2:5" ht="21" customHeight="1"/>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="18">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
@@ -11989,7 +11983,6 @@
       <c r="I76" s="30"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="18">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
@@ -12170,7 +12163,7 @@
       </c>
       <c r="G5" s="51"/>
       <c r="H5" s="81" t="str">
-        <f>"Overdue: "&amp;'_Data'!$AF$15&amp;" invoices"</f>
+        <f>"Overdue: "&amp;'_Data'!$AF$15&amp;IF('_Data'!$AF$15=1," invoice"," invoices")</f>
         <v>Overdue: 0 invoices</v>
       </c>
       <c r="I5" s="81"/>
@@ -13866,7 +13859,6 @@
       <c r="E96" s="30"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="18">
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
@@ -14434,7 +14426,6 @@
     <row r="95" ht="19" customHeight="1"/>
     <row r="96" ht="19" customHeight="1"/>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="46">
     <mergeCell ref="B5:H7"/>
     <mergeCell ref="B8:H9"/>

--- a/products/Catering_Business_Manager_BASIC_Fresh.xlsx
+++ b/products/Catering_Business_Manager_BASIC_Fresh.xlsx
@@ -7203,7 +7203,7 @@
   </mergeCells>
   <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Currency symbol" prompt="Pick a symbol, or type your own (e.g. Rs)." sqref="C9:D9">
-      <formula1>$,€,£,¥,₨,₹,A$,C$,R,kr,CHF</formula1>
+      <formula1>"$,€,£,¥,₨,₹,A$,C$,R,kr,CHF"</formula1>
     </dataValidation>
     <dataValidation type="decimal" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Pick a percentage" error="Enter a share of the price between 0% and 50%." sqref="C11:D11">
       <formula1>0</formula1>
@@ -10513,7 +10513,7 @@
       <formula>$Q8="❌ Cancelled"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="10">
+  <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Event type" prompt="Pick from your list (edit it on Setup)." sqref="F8:F47">
       <formula1>EventTypes</formula1>
     </dataValidation>
@@ -10522,9 +10522,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Client" prompt="Pick a client from the Clients tab (or type a new name and add them there)." sqref="D8:D47">
       <formula1>ClientsList</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not on the menu list" error="That's not one of your priced menu items - continue anyway?" promptTitle="Menu" prompt="Pick a dish from Menu Costing, or type a combination (comma separated)." sqref="H8:H47">
-      <formula1>MenuItems</formula1>
     </dataValidation>
     <dataValidation type="date" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="That's not a date" error="Enter a date between 2000 and 2100." promptTitle="Date" prompt="Type a date, or pick one from the calendar picker." sqref="E8:E47">
       <formula1>36526</formula1>
